--- a/LubanConfig/MiniTemplate/Datas/基础数据/#肉鸽技能数据表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#肉鸽技能数据表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -175,6 +175,82 @@
   </si>
   <si>
     <t>快消大师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肾上腺素1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意外收获（4级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意外收获（5级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意外收获（6级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敢死队1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保持四行1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事不过四1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小小小1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转不动1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐心学习（2级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意外收获（7级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意外收获（8级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意外收获（9级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敢死队2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保持四行2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事不过四2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小小小2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转不动2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肾上腺素2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -208,7 +284,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,12 +294,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -240,19 +310,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -265,34 +329,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -615,17 +673,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="23.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9" style="7"/>
-    <col min="4" max="4" width="14.625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="12.625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="14.25" style="7" customWidth="1"/>
-    <col min="7" max="9" width="21.625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="50.625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="9" style="5"/>
+    <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="5" customWidth="1"/>
+    <col min="7" max="9" width="21.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="50.625" style="6" customWidth="1"/>
     <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -657,7 +715,7 @@
       <c r="I1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="9"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -687,7 +745,7 @@
       <c r="I2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="9"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -703,346 +761,900 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B4" s="14" t="s">
+    <row r="4" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="15">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15">
-        <v>0</v>
-      </c>
-      <c r="E4" s="16">
+      <c r="C4" s="10">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11">
         <v>0.1</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="12">
         <v>1</v>
       </c>
-      <c r="G4" s="15">
-        <v>0</v>
-      </c>
-      <c r="H4" s="15">
+      <c r="G4" s="10">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10">
         <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12">
+        <v>1.125</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" ref="H5:H13" si="0">1/(COUNTA(B:B)-3)</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="10">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12">
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
         <v>0.1</v>
       </c>
-      <c r="I4" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11">
-        <v>1.125</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
-        <f t="shared" ref="H5:H13" si="0">1/(COUNTA(B:B)-3)</f>
+      <c r="F8" s="12">
+        <v>0.88339222614840984</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="F9" s="12">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10">
+        <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
         <v>0.1</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11">
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
+      <c r="F10" s="12">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10">
         <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B7" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="15">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15">
-        <v>0</v>
-      </c>
-      <c r="E7" s="15">
-        <v>0</v>
-      </c>
-      <c r="F7" s="17">
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="G7" s="15">
-        <v>0</v>
-      </c>
-      <c r="H7" s="15">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B8" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="15">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="F8" s="17">
-        <v>0.88339222614840984</v>
-      </c>
-      <c r="G8" s="15">
-        <v>0</v>
-      </c>
-      <c r="H8" s="15">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0</v>
-      </c>
-      <c r="E9" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="F9" s="11">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0</v>
-      </c>
-      <c r="E10" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="F10" s="11">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="4" t="s">
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B11" s="14" t="s">
+    <row r="11" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="15">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15">
-        <v>0</v>
-      </c>
-      <c r="E11" s="15">
-        <v>0</v>
-      </c>
-      <c r="F11" s="17">
+      <c r="C11" s="10">
+        <v>0</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
         <v>1.05</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="10">
         <f>[1]消除倍率计算!$G$202</f>
         <v>0.28499999999999992</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="10">
         <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0.08</v>
+      </c>
+      <c r="H12" s="10">
+        <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10">
+        <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="10">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11">
         <v>0.1</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="F14" s="12">
+        <v>1</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10">
+        <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="10">
+        <v>0</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
+        <v>1.125</v>
+      </c>
+      <c r="G15" s="10">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10">
+        <f t="shared" ref="H15:H23" si="1">1/(COUNTA(B:B)-3)</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="16"/>
+    </row>
+    <row r="16" spans="1:11" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="10">
+        <v>0</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10">
+        <f t="shared" si="1"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B17" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="10">
+        <v>0</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10">
+        <f t="shared" si="1"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="10">
+        <v>0</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0</v>
+      </c>
+      <c r="E18" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0.88339222614840984</v>
+      </c>
+      <c r="G18" s="10">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10">
+        <f t="shared" si="1"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B19" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="10">
+        <v>0</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="F19" s="12">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10">
+        <f t="shared" si="1"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B20" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="10">
+        <v>0</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0</v>
+      </c>
+      <c r="E20" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="F20" s="12">
+        <v>1</v>
+      </c>
+      <c r="G20" s="10">
+        <v>0</v>
+      </c>
+      <c r="H20" s="10">
+        <f t="shared" si="1"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B21" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="10">
+        <v>0</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0</v>
+      </c>
+      <c r="F21" s="12">
+        <v>1.05</v>
+      </c>
+      <c r="G21" s="10">
+        <f>[1]消除倍率计算!$G$202</f>
+        <v>0.28499999999999992</v>
+      </c>
+      <c r="H21" s="10">
+        <f t="shared" si="1"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I21" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J21" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0</v>
-      </c>
-      <c r="D12" s="19">
-        <v>0</v>
-      </c>
-      <c r="E12" s="19">
-        <v>0</v>
-      </c>
-      <c r="F12" s="20">
+    <row r="22" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B22" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>0</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4">
         <v>0.92</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G22" s="10">
         <v>0.08</v>
       </c>
-      <c r="H12" s="15">
-        <f t="shared" si="0"/>
+      <c r="H22" s="10">
+        <f t="shared" si="1"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B23" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0</v>
+      </c>
+      <c r="H23" s="10">
+        <f t="shared" si="1"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B24" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="10">
+        <v>0</v>
+      </c>
+      <c r="D24" s="10">
+        <v>0</v>
+      </c>
+      <c r="E24" s="11">
         <v>0.1</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="F24" s="12">
+        <v>1</v>
+      </c>
+      <c r="G24" s="10">
+        <v>0</v>
+      </c>
+      <c r="H24" s="10">
+        <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B25" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="10">
+        <v>0</v>
+      </c>
+      <c r="D25" s="10">
+        <v>0</v>
+      </c>
+      <c r="E25" s="10">
+        <v>0</v>
+      </c>
+      <c r="F25" s="12">
+        <v>1.125</v>
+      </c>
+      <c r="G25" s="10">
+        <v>0</v>
+      </c>
+      <c r="H25" s="10">
+        <f t="shared" ref="H25:H32" si="2">1/(COUNTA(B:B)-3)</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B26" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="10">
+        <v>0</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0</v>
+      </c>
+      <c r="F26" s="12">
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
+      <c r="H26" s="10">
+        <f t="shared" si="2"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B27" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="10">
+        <v>0</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0</v>
+      </c>
+      <c r="F27" s="12">
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0</v>
+      </c>
+      <c r="H27" s="10">
+        <f t="shared" si="2"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B28" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="10">
+        <v>0</v>
+      </c>
+      <c r="D28" s="10">
+        <v>0</v>
+      </c>
+      <c r="E28" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="F28" s="12">
+        <v>0.88339222614840984</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0</v>
+      </c>
+      <c r="H28" s="10">
+        <f t="shared" si="2"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B29" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="10">
+        <v>0</v>
+      </c>
+      <c r="D29" s="10">
+        <v>0</v>
+      </c>
+      <c r="E29" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="F29" s="12">
+        <v>1</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0</v>
+      </c>
+      <c r="H29" s="10">
+        <f t="shared" si="2"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I29" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J29" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B30" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="10">
+        <v>0</v>
+      </c>
+      <c r="D30" s="10">
+        <v>0</v>
+      </c>
+      <c r="E30" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="F30" s="12">
+        <v>1</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0</v>
+      </c>
+      <c r="H30" s="10">
+        <f t="shared" si="2"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B31" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="10">
+        <v>0</v>
+      </c>
+      <c r="D31" s="10">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10">
+        <v>0</v>
+      </c>
+      <c r="F31" s="12">
+        <v>1.05</v>
+      </c>
+      <c r="G31" s="10">
+        <f>[1]消除倍率计算!$G$202</f>
+        <v>0.28499999999999992</v>
+      </c>
+      <c r="H31" s="10">
+        <f t="shared" si="2"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B32" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>0</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0.08</v>
+      </c>
+      <c r="H32" s="10">
+        <f t="shared" si="2"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7">
-        <v>0</v>
-      </c>
-      <c r="H13" s="7">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="3:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-      <c r="J17" s="4"/>
+    <row r="33" spans="3:10" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#肉鸽技能数据表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#肉鸽技能数据表.xlsx
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="11">
-        <v>1.125</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G4" s="9">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="11">
-        <v>1.1428571428571428</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G5" s="9">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="11">
-        <v>1.1666666666666667</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="G6" s="9">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="11">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="G10" s="9">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="11">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="G11" s="9">
         <v>0</v>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="11">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="G12" s="9">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="11">
-        <v>1.1111111111111112</v>
+        <v>1.05</v>
       </c>
       <c r="G14" s="9">
         <v>0</v>
@@ -1214,7 +1214,8 @@
         <v>1</v>
       </c>
       <c r="G16" s="9">
-        <v>0.14299999999999999</v>
+        <f>0.143/2</f>
+        <v>7.1499999999999994E-2</v>
       </c>
       <c r="H16" s="9">
         <f t="shared" si="0"/>
@@ -1274,8 +1275,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="9">
-        <f t="shared" ref="G18:G24" si="1">0.143*2</f>
-        <v>0.28599999999999998</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="H18" s="9">
         <f t="shared" si="0"/>
@@ -1305,8 +1305,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28599999999999998</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="H19" s="9">
         <f t="shared" si="0"/>
@@ -1336,8 +1335,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28599999999999998</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="H20" s="9">
         <f t="shared" si="0"/>
@@ -1367,8 +1365,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28599999999999998</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="H21" s="9">
         <f t="shared" si="0"/>
@@ -1398,8 +1395,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28599999999999998</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="H22" s="9">
         <f t="shared" si="0"/>
@@ -1429,8 +1425,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28599999999999998</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="H23" s="9">
         <f t="shared" si="0"/>
@@ -1460,8 +1455,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="1"/>
-        <v>0.28599999999999998</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="H24" s="9">
         <f t="shared" si="0"/>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#肉鸽技能数据表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#肉鸽技能数据表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -188,9 +188,6 @@
     <t>冒险主义</t>
   </si>
   <si>
-    <t>迎难而上</t>
-  </si>
-  <si>
     <t>无限火力</t>
   </si>
   <si>
@@ -293,18 +290,10 @@
     <t>城堡最大血量增加10%，士兵的攻击力提高10%</t>
   </si>
   <si>
-    <t>自动下5个小方块帮助消除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>XX型方块上可以多站1个小兵</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>献祭I形方块，全体小兵+30%生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>小兵移动速度+20%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -314,6 +303,10 @@
   </si>
   <si>
     <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动下10个小方块帮助消除</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -453,11 +446,6 @@
       <sheetData sheetId="6">
         <row r="92">
           <cell r="D92">
-            <v>0.86</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="E159">
             <v>0.86</v>
           </cell>
         </row>
@@ -735,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -823,7 +811,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>11</v>
@@ -853,10 +841,10 @@
       </c>
       <c r="H4" s="9">
         <f t="shared" ref="H4:H35" si="0">1/(COUNTA(B:B)-3)</f>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>12</v>
@@ -883,10 +871,10 @@
       </c>
       <c r="H5" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>13</v>
@@ -913,10 +901,10 @@
       </c>
       <c r="H6" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>14</v>
@@ -943,10 +931,10 @@
       </c>
       <c r="H7" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>15</v>
@@ -973,10 +961,10 @@
       </c>
       <c r="H8" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>16</v>
@@ -1003,13 +991,13 @@
       </c>
       <c r="H9" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1033,13 +1021,13 @@
       </c>
       <c r="H10" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1063,13 +1051,13 @@
       </c>
       <c r="H11" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1093,13 +1081,13 @@
       </c>
       <c r="H12" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1123,13 +1111,13 @@
       </c>
       <c r="H13" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>22</v>
@@ -1156,13 +1144,13 @@
       </c>
       <c r="H14" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K14" s="14"/>
     </row>
@@ -1187,19 +1175,19 @@
       </c>
       <c r="H15" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K15" s="14"/>
     </row>
     <row r="16" spans="1:11" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B16" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -1219,13 +1207,13 @@
       </c>
       <c r="H16" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1249,13 +1237,13 @@
       </c>
       <c r="H17" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1279,13 +1267,13 @@
       </c>
       <c r="H18" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1309,13 +1297,13 @@
       </c>
       <c r="H19" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1339,13 +1327,13 @@
       </c>
       <c r="H20" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1369,13 +1357,13 @@
       </c>
       <c r="H21" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1399,13 +1387,13 @@
       </c>
       <c r="H22" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1429,13 +1417,13 @@
       </c>
       <c r="H23" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1459,13 +1447,13 @@
       </c>
       <c r="H24" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1489,13 +1477,13 @@
       </c>
       <c r="H25" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1520,13 +1508,13 @@
       </c>
       <c r="H26" s="9">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1534,30 +1522,29 @@
         <v>46</v>
       </c>
       <c r="C27" s="10">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="D27" s="10">
         <v>0</v>
       </c>
       <c r="E27" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F27" s="11">
-        <f>[1]消除倍率计算!$E$159</f>
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="G27" s="9">
         <v>0</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1565,13 +1552,13 @@
         <v>47</v>
       </c>
       <c r="C28" s="10">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="D28" s="10">
         <v>0</v>
       </c>
       <c r="E28" s="10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="11">
         <v>1</v>
@@ -1580,11 +1567,11 @@
         <v>0</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J28" s="12" t="s">
         <v>67</v>
@@ -1595,7 +1582,7 @@
         <v>48</v>
       </c>
       <c r="C29" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D29" s="10">
         <v>0</v>
@@ -1610,11 +1597,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J29" s="12" t="s">
         <v>68</v>
@@ -1625,13 +1612,13 @@
         <v>49</v>
       </c>
       <c r="C30" s="10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D30" s="10">
         <v>0</v>
       </c>
       <c r="E30" s="10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F30" s="11">
         <v>1</v>
@@ -1640,11 +1627,11 @@
         <v>0</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J30" s="12" t="s">
         <v>69</v>
@@ -1658,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="D31" s="10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E31" s="10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="11">
         <v>1</v>
@@ -1670,11 +1657,11 @@
         <v>0</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J31" s="12" t="s">
         <v>70</v>
@@ -1688,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="10">
         <v>0</v>
@@ -1700,14 +1687,14 @@
         <v>0</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="2:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
@@ -1730,14 +1717,14 @@
         <v>0</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
@@ -1748,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E34" s="10">
         <v>0</v>
@@ -1760,44 +1747,14 @@
         <v>0</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <f>1/(COUNTA(B:B)-3)</f>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B35" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="10">
-        <v>0</v>
-      </c>
-      <c r="D35" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="E35" s="10">
-        <v>0</v>
-      </c>
-      <c r="F35" s="11">
-        <v>1</v>
-      </c>
-      <c r="G35" s="9">
-        <v>0</v>
-      </c>
-      <c r="H35" s="9">
-        <f t="shared" si="0"/>
-        <v>3.125E-2</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
